--- a/output_files/HOLD MID_WID.xlsx
+++ b/output_files/HOLD MID_WID.xlsx
@@ -37,19 +37,19 @@
     <t>1139089</t>
   </si>
   <si>
+    <t>1181484_925160</t>
+  </si>
+  <si>
     <t>1182161</t>
   </si>
   <si>
-    <t>1183547</t>
-  </si>
-  <si>
     <t>Euronet</t>
   </si>
   <si>
+    <t>Wow Momo</t>
+  </si>
+  <si>
     <t>Euronet Services</t>
-  </si>
-  <si>
-    <t>Gvs 3rd Party Offers</t>
   </si>
 </sst>
 </file>
@@ -415,10 +415,10 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>11131941.77</v>
+        <v>9147611.029999999</v>
       </c>
       <c r="E2">
-        <v>202334.77</v>
+        <v>170326.42</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -426,16 +426,16 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>8302697</v>
+        <v>8303177</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>1424074.46</v>
+        <v>161.97</v>
       </c>
       <c r="E3">
-        <v>34359.19</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -443,16 +443,16 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>8303160</v>
+        <v>8302697</v>
       </c>
       <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>-5.4</v>
+        <v>1030966.03</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>26038.15</v>
       </c>
     </row>
   </sheetData>
